--- a/public/COA_DMR_Monthly_Report.xlsx
+++ b/public/COA_DMR_Monthly_Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboards Projects\Follow-Up Sheets Dashboard\follow-up-sheets-dashboard V3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboards Projects\Follow-Up Sheets Dashboard\follow-up-sheets-dashboard V3\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D173A7BA-1857-4A09-9229-D08F97D9597C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609F7F50-F2FB-4BBE-BE10-792526481412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,7 +335,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,20 +418,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -453,7 +439,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="49">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -1033,37 +1019,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1075,112 +1035,10 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="46" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="46" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1453,14 +1311,47 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1873,706 +1764,706 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="85"/>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
+      <c r="A1" s="51"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
     </row>
     <row r="2" spans="1:17" ht="100.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="116"/>
-      <c r="B2" s="117"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="123" t="s">
+      <c r="A2" s="82"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="121"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="87"/>
     </row>
     <row r="3" spans="1:17" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="122"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
     </row>
     <row r="4" spans="1:17" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="126" t="s">
+      <c r="A4" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
-      <c r="N4" s="127"/>
-      <c r="O4" s="127"/>
-      <c r="P4" s="127"/>
-      <c r="Q4" s="128"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93"/>
+      <c r="P4" s="93"/>
+      <c r="Q4" s="94"/>
     </row>
     <row r="5" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="129" t="s">
+      <c r="B5" s="74"/>
+      <c r="C5" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="106" t="s">
+      <c r="D5" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="100" t="s">
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="J5" s="101"/>
-      <c r="K5" s="101"/>
-      <c r="L5" s="101"/>
-      <c r="M5" s="101"/>
-      <c r="N5" s="101"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="82" t="s">
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="112"/>
+      <c r="Q5" s="78"/>
     </row>
     <row r="6" spans="1:17" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="115"/>
-      <c r="B6" s="111"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="104"/>
-      <c r="O6" s="105"/>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="113"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="79"/>
     </row>
     <row r="7" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="84"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="84"/>
-      <c r="K7" s="84"/>
-      <c r="L7" s="84"/>
-      <c r="M7" s="84"/>
-      <c r="N7" s="84"/>
-      <c r="O7" s="84"/>
-      <c r="P7" s="84"/>
-      <c r="Q7" s="84"/>
+      <c r="A7" s="50"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="50"/>
     </row>
     <row r="8" spans="1:17" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="87"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="87"/>
-      <c r="E8" s="87"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="87"/>
-      <c r="J8" s="87"/>
-      <c r="K8" s="87"/>
-      <c r="L8" s="87"/>
-      <c r="M8" s="87"/>
-      <c r="N8" s="87"/>
-      <c r="O8" s="87"/>
-      <c r="P8" s="87"/>
-      <c r="Q8" s="88"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="53"/>
+      <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="1:17" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="89" t="s">
+      <c r="C9" s="64"/>
+      <c r="D9" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="91" t="s">
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="92"/>
-      <c r="K9" s="92"/>
-      <c r="L9" s="92"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="93"/>
-      <c r="O9" s="91" t="s">
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="59"/>
+      <c r="O9" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="P9" s="92"/>
-      <c r="Q9" s="94"/>
+      <c r="P9" s="58"/>
+      <c r="Q9" s="60"/>
     </row>
     <row r="10" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>1</v>
       </c>
-      <c r="B10" s="99" t="s">
+      <c r="B10" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="51" t="s">
+      <c r="C10" s="65"/>
+      <c r="D10" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="95" t="s">
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="95"/>
-      <c r="M10" s="95"/>
-      <c r="N10" s="95"/>
-      <c r="O10" s="95"/>
-      <c r="P10" s="95"/>
-      <c r="Q10" s="96"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="62"/>
     </row>
     <row r="11" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>2</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="51" t="s">
+      <c r="C11" s="19"/>
+      <c r="D11" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51" t="s">
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="52"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="18"/>
     </row>
     <row r="12" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>3</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="53"/>
-      <c r="D12" s="51" t="s">
+      <c r="C12" s="19"/>
+      <c r="D12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51" t="s">
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="52"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="18"/>
     </row>
     <row r="13" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>4</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="53"/>
-      <c r="D13" s="51" t="s">
+      <c r="C13" s="19"/>
+      <c r="D13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51" t="s">
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="51"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="52"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="18"/>
     </row>
     <row r="14" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>5</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="53"/>
-      <c r="D14" s="51" t="s">
+      <c r="C14" s="19"/>
+      <c r="D14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51" t="s">
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="51"/>
-      <c r="K14" s="51"/>
-      <c r="L14" s="51"/>
-      <c r="M14" s="51"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="52"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="18"/>
     </row>
     <row r="15" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>6</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="53"/>
-      <c r="D15" s="51" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51" t="s">
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="51"/>
-      <c r="M15" s="51"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="52"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="18"/>
     </row>
     <row r="16" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>7</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="53"/>
-      <c r="D16" s="51" t="s">
+      <c r="C16" s="19"/>
+      <c r="D16" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51" t="s">
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="51"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="52"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="18"/>
     </row>
     <row r="17" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>8</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="53"/>
-      <c r="D17" s="51" t="s">
+      <c r="C17" s="19"/>
+      <c r="D17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51" t="s">
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="51"/>
-      <c r="M17" s="51"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="52"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="18"/>
     </row>
     <row r="18" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>9</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="53"/>
-      <c r="D18" s="51" t="s">
+      <c r="C18" s="19"/>
+      <c r="D18" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51" t="s">
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="52"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="18"/>
     </row>
     <row r="19" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>10</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="51" t="s">
+      <c r="C19" s="19"/>
+      <c r="D19" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51" t="s">
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="51"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="52"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="18"/>
     </row>
     <row r="20" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>11</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="53"/>
-      <c r="D20" s="51" t="s">
+      <c r="C20" s="19"/>
+      <c r="D20" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51" t="s">
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="52"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="18"/>
     </row>
     <row r="21" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>12</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="51" t="s">
+      <c r="C21" s="19"/>
+      <c r="D21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51" t="s">
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="51"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="52"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="18"/>
     </row>
     <row r="22" spans="1:27" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>13</v>
       </c>
-      <c r="B22" s="53" t="s">
+      <c r="B22" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="51" t="s">
+      <c r="C22" s="19"/>
+      <c r="D22" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51" t="s">
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="52"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="18"/>
     </row>
     <row r="23" spans="1:27" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>14</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="51" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51" t="s">
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="52"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="18"/>
     </row>
     <row r="24" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>15</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="53"/>
-      <c r="D24" s="51" t="s">
+      <c r="C24" s="19"/>
+      <c r="D24" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51" t="s">
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="52"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="18"/>
     </row>
     <row r="25" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>16</v>
       </c>
-      <c r="B25" s="53" t="s">
+      <c r="B25" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="53"/>
-      <c r="D25" s="51" t="s">
+      <c r="C25" s="19"/>
+      <c r="D25" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51" t="s">
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
-      <c r="L25" s="51"/>
-      <c r="M25" s="51"/>
-      <c r="N25" s="51"/>
-      <c r="O25" s="51"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="52"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="18"/>
     </row>
     <row r="26" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>17</v>
       </c>
-      <c r="B26" s="53" t="s">
+      <c r="B26" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="51" t="s">
+      <c r="C26" s="19"/>
+      <c r="D26" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51" t="s">
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="51"/>
-      <c r="M26" s="51"/>
-      <c r="N26" s="51"/>
-      <c r="O26" s="51"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="52"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="18"/>
     </row>
     <row r="27" spans="1:27" ht="80.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="22">
+      <c r="A27" s="6">
         <v>18</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42" t="s">
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="49"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="50"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="16"/>
     </row>
     <row r="28" spans="1:27" s="1" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="45"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="11"/>
       <c r="R28"/>
       <c r="S28"/>
       <c r="T28"/>
@@ -2585,25 +2476,25 @@
       <c r="AA28"/>
     </row>
     <row r="29" spans="1:27" s="1" customFormat="1" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="48"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="14"/>
       <c r="R29"/>
       <c r="S29"/>
       <c r="T29"/>
@@ -2616,49 +2507,49 @@
       <c r="AA29"/>
     </row>
     <row r="30" spans="1:27" s="1" customFormat="1" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="79" t="s">
+      <c r="B30" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="57" t="s">
+      <c r="C30" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="75" t="s">
+      <c r="D30" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="77" t="s">
+      <c r="E30" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="132" t="s">
+      <c r="F30" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="G30" s="133"/>
-      <c r="H30" s="132" t="s">
+      <c r="G30" s="98"/>
+      <c r="H30" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="I30" s="133"/>
-      <c r="J30" s="132" t="s">
+      <c r="I30" s="98"/>
+      <c r="J30" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="K30" s="133"/>
-      <c r="L30" s="78" t="s">
+      <c r="K30" s="98"/>
+      <c r="L30" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="M30" s="78" t="s">
+      <c r="M30" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="N30" s="78" t="s">
+      <c r="N30" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="O30" s="78" t="s">
+      <c r="O30" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="P30" s="77" t="s">
+      <c r="P30" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="Q30" s="78" t="s">
+      <c r="Q30" s="44" t="s">
         <v>91</v>
       </c>
       <c r="R30"/>
@@ -2672,36 +2563,36 @@
       <c r="Z30"/>
       <c r="AA30"/>
     </row>
-    <row r="31" spans="1:27" s="1" customFormat="1" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="57"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="7" t="s">
+    <row r="31" spans="1:27" s="1" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="23"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K31" s="7" t="s">
+      <c r="K31" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="L31" s="81"/>
-      <c r="M31" s="81"/>
-      <c r="N31" s="81"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="78"/>
-      <c r="Q31" s="81"/>
+      <c r="L31" s="47"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="47"/>
+      <c r="O31" s="47"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="47"/>
       <c r="R31"/>
       <c r="S31"/>
       <c r="T31"/>
@@ -2714,23 +2605,23 @@
       <c r="AA31"/>
     </row>
     <row r="32" spans="1:27" s="1" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="25"/>
+      <c r="A32" s="100"/>
+      <c r="B32" s="101"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="106"/>
+      <c r="H32" s="102"/>
+      <c r="I32" s="102"/>
+      <c r="J32" s="102"/>
+      <c r="K32" s="102"/>
+      <c r="L32" s="107"/>
+      <c r="M32" s="108"/>
+      <c r="N32" s="108"/>
+      <c r="O32" s="108"/>
+      <c r="P32" s="104"/>
+      <c r="Q32" s="109"/>
       <c r="R32"/>
       <c r="S32"/>
       <c r="T32"/>
@@ -2743,23 +2634,23 @@
       <c r="AA32"/>
     </row>
     <row r="33" spans="1:27" s="1" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="26"/>
+      <c r="A33" s="100"/>
+      <c r="B33" s="101"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="106"/>
+      <c r="H33" s="102"/>
+      <c r="I33" s="102"/>
+      <c r="J33" s="102"/>
+      <c r="K33" s="102"/>
+      <c r="L33" s="107"/>
+      <c r="M33" s="108"/>
+      <c r="N33" s="108"/>
+      <c r="O33" s="108"/>
+      <c r="P33" s="104"/>
+      <c r="Q33" s="109"/>
       <c r="R33"/>
       <c r="S33"/>
       <c r="T33"/>
@@ -2772,23 +2663,23 @@
       <c r="AA33"/>
     </row>
     <row r="34" spans="1:27" s="1" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="26"/>
+      <c r="A34" s="100"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="102"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="102"/>
+      <c r="L34" s="107"/>
+      <c r="M34" s="108"/>
+      <c r="N34" s="108"/>
+      <c r="O34" s="108"/>
+      <c r="P34" s="104"/>
+      <c r="Q34" s="109"/>
       <c r="R34"/>
       <c r="S34"/>
       <c r="T34"/>
@@ -2801,23 +2692,23 @@
       <c r="AA34"/>
     </row>
     <row r="35" spans="1:27" s="1" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="26"/>
+      <c r="A35" s="100"/>
+      <c r="B35" s="101"/>
+      <c r="C35" s="102"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="102"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="102"/>
+      <c r="K35" s="102"/>
+      <c r="L35" s="107"/>
+      <c r="M35" s="108"/>
+      <c r="N35" s="108"/>
+      <c r="O35" s="108"/>
+      <c r="P35" s="104"/>
+      <c r="Q35" s="109"/>
       <c r="R35"/>
       <c r="S35"/>
       <c r="T35"/>
@@ -2830,332 +2721,332 @@
       <c r="AA35"/>
     </row>
     <row r="36" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="12"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="26"/>
+      <c r="A36" s="100"/>
+      <c r="B36" s="101"/>
+      <c r="C36" s="102"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="104"/>
+      <c r="F36" s="105"/>
+      <c r="G36" s="106"/>
+      <c r="H36" s="102"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="102"/>
+      <c r="K36" s="102"/>
+      <c r="L36" s="107"/>
+      <c r="M36" s="108"/>
+      <c r="N36" s="108"/>
+      <c r="O36" s="108"/>
+      <c r="P36" s="104"/>
+      <c r="Q36" s="109"/>
     </row>
     <row r="37" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="26"/>
+      <c r="A37" s="100"/>
+      <c r="B37" s="101"/>
+      <c r="C37" s="102"/>
+      <c r="D37" s="103"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="105"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="101"/>
+      <c r="I37" s="102"/>
+      <c r="J37" s="102"/>
+      <c r="K37" s="102"/>
+      <c r="L37" s="107"/>
+      <c r="M37" s="108"/>
+      <c r="N37" s="107"/>
+      <c r="O37" s="108"/>
+      <c r="P37" s="104"/>
+      <c r="Q37" s="109"/>
     </row>
     <row r="38" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="12"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="26"/>
+      <c r="A38" s="100"/>
+      <c r="B38" s="101"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="105"/>
+      <c r="G38" s="106"/>
+      <c r="H38" s="101"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="102"/>
+      <c r="K38" s="102"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="108"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="108"/>
+      <c r="P38" s="104"/>
+      <c r="Q38" s="109"/>
     </row>
     <row r="39" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="14"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="26"/>
+      <c r="A39" s="100"/>
+      <c r="B39" s="101"/>
+      <c r="C39" s="102"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="105"/>
+      <c r="G39" s="106"/>
+      <c r="H39" s="101"/>
+      <c r="I39" s="102"/>
+      <c r="J39" s="102"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="107"/>
+      <c r="M39" s="108"/>
+      <c r="N39" s="107"/>
+      <c r="O39" s="108"/>
+      <c r="P39" s="104"/>
+      <c r="Q39" s="109"/>
     </row>
     <row r="40" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="26"/>
+      <c r="A40" s="100"/>
+      <c r="B40" s="101"/>
+      <c r="C40" s="102"/>
+      <c r="D40" s="103"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="105"/>
+      <c r="G40" s="106"/>
+      <c r="H40" s="101"/>
+      <c r="I40" s="102"/>
+      <c r="J40" s="102"/>
+      <c r="K40" s="102"/>
+      <c r="L40" s="107"/>
+      <c r="M40" s="108"/>
+      <c r="N40" s="107"/>
+      <c r="O40" s="108"/>
+      <c r="P40" s="104"/>
+      <c r="Q40" s="109"/>
     </row>
     <row r="41" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="12"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="27"/>
+      <c r="A41" s="100"/>
+      <c r="B41" s="108"/>
+      <c r="C41" s="102"/>
+      <c r="D41" s="103"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="106"/>
+      <c r="H41" s="101"/>
+      <c r="I41" s="102"/>
+      <c r="J41" s="102"/>
+      <c r="K41" s="102"/>
+      <c r="L41" s="107"/>
+      <c r="M41" s="108"/>
+      <c r="N41" s="107"/>
+      <c r="O41" s="108"/>
+      <c r="P41" s="104"/>
+      <c r="Q41" s="110"/>
     </row>
     <row r="42" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="12"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="26"/>
+      <c r="A42" s="100"/>
+      <c r="B42" s="101"/>
+      <c r="C42" s="102"/>
+      <c r="D42" s="103"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="106"/>
+      <c r="H42" s="101"/>
+      <c r="I42" s="102"/>
+      <c r="J42" s="102"/>
+      <c r="K42" s="102"/>
+      <c r="L42" s="107"/>
+      <c r="M42" s="108"/>
+      <c r="N42" s="107"/>
+      <c r="O42" s="108"/>
+      <c r="P42" s="104"/>
+      <c r="Q42" s="109"/>
     </row>
     <row r="43" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="12"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="14"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="14"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="26"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="101"/>
+      <c r="C43" s="102"/>
+      <c r="D43" s="103"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="105"/>
+      <c r="G43" s="106"/>
+      <c r="H43" s="101"/>
+      <c r="I43" s="102"/>
+      <c r="J43" s="102"/>
+      <c r="K43" s="102"/>
+      <c r="L43" s="107"/>
+      <c r="M43" s="108"/>
+      <c r="N43" s="107"/>
+      <c r="O43" s="108"/>
+      <c r="P43" s="104"/>
+      <c r="Q43" s="109"/>
     </row>
     <row r="44" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="12"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="14"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="26"/>
+      <c r="A44" s="100"/>
+      <c r="B44" s="101"/>
+      <c r="C44" s="102"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="106"/>
+      <c r="H44" s="101"/>
+      <c r="I44" s="102"/>
+      <c r="J44" s="102"/>
+      <c r="K44" s="102"/>
+      <c r="L44" s="107"/>
+      <c r="M44" s="108"/>
+      <c r="N44" s="107"/>
+      <c r="O44" s="108"/>
+      <c r="P44" s="104"/>
+      <c r="Q44" s="109"/>
     </row>
     <row r="45" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="14"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="14"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="26"/>
+      <c r="A45" s="100"/>
+      <c r="B45" s="101"/>
+      <c r="C45" s="102"/>
+      <c r="D45" s="103"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="106"/>
+      <c r="H45" s="101"/>
+      <c r="I45" s="102"/>
+      <c r="J45" s="102"/>
+      <c r="K45" s="102"/>
+      <c r="L45" s="107"/>
+      <c r="M45" s="108"/>
+      <c r="N45" s="107"/>
+      <c r="O45" s="108"/>
+      <c r="P45" s="104"/>
+      <c r="Q45" s="109"/>
     </row>
     <row r="46" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="14"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="26"/>
-    </row>
-    <row r="47" spans="1:27" ht="77.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="28"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="36"/>
-      <c r="M47" s="31"/>
-      <c r="N47" s="36"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="37"/>
+      <c r="A46" s="100"/>
+      <c r="B46" s="101"/>
+      <c r="C46" s="102"/>
+      <c r="D46" s="103"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="106"/>
+      <c r="H46" s="101"/>
+      <c r="I46" s="102"/>
+      <c r="J46" s="102"/>
+      <c r="K46" s="102"/>
+      <c r="L46" s="107"/>
+      <c r="M46" s="108"/>
+      <c r="N46" s="107"/>
+      <c r="O46" s="108"/>
+      <c r="P46" s="104"/>
+      <c r="Q46" s="109"/>
+    </row>
+    <row r="47" spans="1:27" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="100"/>
+      <c r="B47" s="101"/>
+      <c r="C47" s="102"/>
+      <c r="D47" s="103"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="106"/>
+      <c r="H47" s="101"/>
+      <c r="I47" s="102"/>
+      <c r="J47" s="102"/>
+      <c r="K47" s="102"/>
+      <c r="L47" s="107"/>
+      <c r="M47" s="108"/>
+      <c r="N47" s="107"/>
+      <c r="O47" s="108"/>
+      <c r="P47" s="104"/>
+      <c r="Q47" s="109"/>
     </row>
     <row r="48" spans="1:27" ht="73.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="60" t="s">
+      <c r="A48" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="61"/>
-      <c r="C48" s="61"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="61"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="61"/>
-      <c r="I48" s="61"/>
-      <c r="J48" s="61"/>
-      <c r="K48" s="61"/>
-      <c r="L48" s="61"/>
-      <c r="M48" s="61"/>
-      <c r="N48" s="61"/>
-      <c r="O48" s="61"/>
-      <c r="P48" s="61"/>
-      <c r="Q48" s="62"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
+      <c r="K48" s="27"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="27"/>
+      <c r="P48" s="27"/>
+      <c r="Q48" s="28"/>
     </row>
     <row r="49" spans="1:17" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="68" t="s">
+      <c r="A49" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B49" s="69"/>
-      <c r="C49" s="69"/>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="73" t="s">
+      <c r="B49" s="35"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="G49" s="73"/>
-      <c r="H49" s="73"/>
-      <c r="I49" s="73"/>
-      <c r="J49" s="73"/>
-      <c r="K49" s="73"/>
-      <c r="L49" s="73"/>
-      <c r="M49" s="73"/>
-      <c r="N49" s="73"/>
-      <c r="O49" s="73"/>
-      <c r="P49" s="73"/>
-      <c r="Q49" s="74"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="39"/>
+      <c r="K49" s="39"/>
+      <c r="L49" s="39"/>
+      <c r="M49" s="39"/>
+      <c r="N49" s="39"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="39"/>
+      <c r="Q49" s="40"/>
     </row>
     <row r="50" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="70" t="s">
+      <c r="A50" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B50" s="63"/>
-      <c r="C50" s="63"/>
-      <c r="D50" s="63" t="s">
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="E50" s="63"/>
-      <c r="F50" s="63" t="s">
+      <c r="E50" s="29"/>
+      <c r="F50" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G50" s="63"/>
-      <c r="H50" s="63"/>
-      <c r="I50" s="63" t="s">
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="J50" s="63"/>
-      <c r="K50" s="63"/>
-      <c r="L50" s="63"/>
-      <c r="M50" s="54" t="s">
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
+      <c r="L50" s="29"/>
+      <c r="M50" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="N50" s="55"/>
-      <c r="O50" s="55"/>
-      <c r="P50" s="63" t="s">
+      <c r="N50" s="21"/>
+      <c r="O50" s="21"/>
+      <c r="P50" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="Q50" s="64"/>
+      <c r="Q50" s="30"/>
     </row>
     <row r="51" spans="1:17" ht="201" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="71" t="s">
+      <c r="A51" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="59"/>
-      <c r="C51" s="72"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
-      <c r="F51" s="65" t="s">
+      <c r="B51" s="25"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="G51" s="65"/>
-      <c r="H51" s="65"/>
-      <c r="I51" s="65"/>
-      <c r="J51" s="65"/>
-      <c r="K51" s="65"/>
-      <c r="L51" s="65"/>
-      <c r="M51" s="58" t="s">
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="31"/>
+      <c r="M51" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="N51" s="59"/>
-      <c r="O51" s="59"/>
-      <c r="P51" s="65"/>
-      <c r="Q51" s="66"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="25"/>
+      <c r="P51" s="31"/>
+      <c r="Q51" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="121">
@@ -3281,11 +3172,6 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D26:H26"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P32:Q47" xr:uid="{BA868367-B347-4E9B-8D13-E66AA72372C2}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="30" fitToWidth="2" orientation="landscape" verticalDpi="4294967295" r:id="rId1"/>
   <headerFooter>
